--- a/data/decisions.xlsx
+++ b/data/decisions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,35 +1544,107 @@
           <t>2026-07-17 10:59:57</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="n">
+        <v>561380</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-17 14:45:01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>561380</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-17 14:55:01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>561380</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>电网设备ETF</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
         </is>
       </c>
-      <c r="H32" t="b">
+      <c r="H34" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/decisions.xlsx
+++ b/data/decisions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1616,35 +1616,71 @@
           <t>2026-07-17 14:55:01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="n">
+        <v>561380</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:16:43</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>561380</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>电网设备ETF</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
         </is>
       </c>
-      <c r="H34" t="b">
+      <c r="H35" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/decisions.xlsx
+++ b/data/decisions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,35 +1652,71 @@
           <t>2026-07-17 15:16:43</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" t="n">
+        <v>561380</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:21:12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>561380</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>电网设备ETF</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>WAIT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>连续下跌 3 个交易日；最新价格仍处于近10个交易日低位；短期下跌尚未停止，默认不加仓</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>相对上一笔买入价已回撤 10.96%；但尚未出现横盘或反转确认</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
         <v>0</v>
       </c>
     </row>
